--- a/Master_Section_Report_2026_27.xlsx
+++ b/Master_Section_Report_2026_27.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -949,7 +949,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>AP Computer Science Principles</t>
+          <t>Web Design</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>494</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>Applied Programming</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -1532,11 +1532,11 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Applied Programming</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1590,29 +1590,29 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>491</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>AP Computer Science Principles</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1638,19 +1638,19 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Algebra II/Trig H</t>
+          <t>AP Calc AB</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1752,19 +1752,19 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AP Calc AB</t>
+          <t>Algebra II/Trig H</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -2132,19 +2132,19 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -2279,24 +2279,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -2355,24 +2355,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2398,19 +2398,19 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Forensics</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -2444,11 +2444,11 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Sports Medicine</t>
+          <t>Forensics</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2474,19 +2474,19 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -2520,11 +2520,11 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
@@ -2558,11 +2558,11 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -2596,11 +2596,11 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Market Concepts</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -2621,24 +2621,24 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>Bloomberg Market Concepts</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -2735,24 +2735,24 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
@@ -2811,24 +2811,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3006,19 +3006,19 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Driver's Ed/PE</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
@@ -3039,24 +3039,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Driver's Ed/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>AP Seminar</t>
+          <t>Composition &amp; Literature H</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Composition &amp; Literature H</t>
+          <t>AP Seminar</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -3888,11 +3888,11 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Adv Painting</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
@@ -3926,11 +3926,11 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>Adv Drawing</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
@@ -3964,11 +3964,11 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Adv Drawing</t>
+          <t>Studio Art II</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -4027,24 +4027,24 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Studio Art II</t>
+          <t>Studio Art III</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4098,29 +4098,29 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>249</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Studio Art III</t>
+          <t>Adv Painting</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="H97" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H99" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="H101" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105">
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="H105" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="H107" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -4554,29 +4554,29 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>AP Business with Personal Finance</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
@@ -4610,11 +4610,11 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
         </is>
       </c>
       <c r="H109" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
+          <t>Business Concepts</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
@@ -4673,24 +4673,24 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Business Concepts</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
         </is>
       </c>
       <c r="H111" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
@@ -4724,11 +4724,11 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
+          <t>Business Concepts</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
@@ -4762,11 +4762,11 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>Business Concepts</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
         </is>
       </c>
       <c r="H113" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4792,19 +4792,19 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
+          <t>Business Concepts</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -4820,29 +4820,29 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Business Concepts</t>
+          <t>AP Business with Personal Finance</t>
         </is>
       </c>
       <c r="H115" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="H117" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="H121" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5096,19 +5096,19 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>British Literature H</t>
+          <t>AP English Language</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="H123" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5172,15 +5172,15 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>AP English Language</t>
+          <t>British Literature H</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
@@ -5294,11 +5294,11 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Calculus H</t>
         </is>
       </c>
       <c r="H127" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
@@ -5332,11 +5332,11 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>Calculus H</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -5362,19 +5362,19 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>Calculus H</t>
+          <t>Algebra II/Trig</t>
         </is>
       </c>
       <c r="H129" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5400,19 +5400,19 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Algebra II/Trig</t>
+          <t>Calculus H</t>
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="H131" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="H133" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135">
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="H135" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136">
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="H139" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="H143" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145">
@@ -5965,24 +5965,24 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Catholic Social Teaching</t>
+          <t>Theology 11</t>
         </is>
       </c>
       <c r="H145" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
@@ -6074,29 +6074,29 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Theology 11</t>
+          <t>Catholic Social Teaching</t>
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="H149" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="H151" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="H153" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154">
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="H155" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156">
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="H157" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="H161" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>412</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
@@ -6738,11 +6738,11 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Algebra I</t>
         </is>
       </c>
       <c r="H165" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -6806,19 +6806,19 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>Algebra I</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="H167" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H169" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -6920,19 +6920,19 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>Earth Science</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="H171" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -6996,19 +6996,19 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Earth Science</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="H173" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7072,19 +7072,19 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Academic Support</t>
+          <t>Composition &amp; Literature</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F175" s="4" t="n">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Composition &amp; Literature</t>
+          <t>Academic Support</t>
         </is>
       </c>
       <c r="H175" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="H176" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         </is>
       </c>
       <c r="H177" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="H180" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="H183" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184">
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185">
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="H185" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186">
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="H187" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>AP Macroeconomics</t>
+          <t>AP Statistics</t>
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189">
@@ -7632,29 +7632,29 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>AP Microeconomics</t>
+          <t>AP Macroeconomics</t>
         </is>
       </c>
       <c r="H189" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190">
@@ -7670,25 +7670,25 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>AP Statistics</t>
+          <t>AP Macroeconomics</t>
         </is>
       </c>
       <c r="H190" s="2" t="n">
@@ -7708,17 +7708,17 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F191" s="4" t="n">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>AP Macroeconomics</t>
+          <t>AP Microeconomics</t>
         </is>
       </c>
       <c r="H191" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193">
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H193" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="194">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="H195" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="197">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="H197" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="H203" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="204">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205">
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="H205" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206">
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H207" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208">
@@ -8359,24 +8359,24 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>Spirituality of Vocation</t>
+          <t>Theology 11</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="H209" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210">
@@ -8430,29 +8430,29 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>Theology 11</t>
+          <t>Spirituality of Vocation</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211">
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="H211" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="H215" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="216">
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="H219" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="H223" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="H225" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -9276,19 +9276,19 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>American Literature</t>
+          <t>Academic Support</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -9314,19 +9314,19 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F233" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>American Literature</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>Academic Support</t>
-        </is>
-      </c>
-      <c r="H233" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="234">
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="H235" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="H236" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="H237" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="H241" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242">
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="H243" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -9732,19 +9732,19 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F244" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>Robotics Design</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>Robotics Engineering</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="245">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="H245" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -9803,24 +9803,24 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>Robotics Design</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="H247" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248">
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="H248" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249">
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="H249" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="H251" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="252">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="253">
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="H253" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="254">
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="H257" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -10302,19 +10302,19 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>332</t>
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Italian II</t>
+          <t>Italian III</t>
         </is>
       </c>
       <c r="H259" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="260">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -10378,19 +10378,19 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Italian III</t>
+          <t>Italian II</t>
         </is>
       </c>
       <c r="H261" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="262">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="H262" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="H265" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="H266" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267">
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="269">
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="273">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H273" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="274">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="H275" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="276">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="H276" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="277">
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="H277" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278">
@@ -11024,19 +11024,19 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Algebra I</t>
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279">
@@ -11062,19 +11062,19 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F279" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Algebra I</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="H279" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280">
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="H281" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="282">
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="H282" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -11416,7 +11416,7 @@
         </is>
       </c>
       <c r="H288" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="H289" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="H290" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="F291" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="H291" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="H292" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="H293" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="H294" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="295">
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="H295" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="H296" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -11784,19 +11784,19 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>World History H</t>
+          <t>AP World History</t>
         </is>
       </c>
       <c r="H298" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="299">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F299" s="4" t="n">
@@ -11830,11 +11830,11 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>AP World History</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="H299" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F300" s="2" t="n">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>AP World History</t>
+          <t>World History H</t>
         </is>
       </c>
       <c r="H300" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="301">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F301" s="4" t="n">
@@ -11906,11 +11906,11 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>AP European History</t>
+          <t>AP World History</t>
         </is>
       </c>
       <c r="H301" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
@@ -11944,11 +11944,11 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>AP European History</t>
         </is>
       </c>
       <c r="H302" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="303">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="F303" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="H303" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>331</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
@@ -12020,11 +12020,11 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>Spanish III</t>
+          <t>Spanish III H</t>
         </is>
       </c>
       <c r="H304" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="305">
@@ -12054,7 +12054,7 @@
         </is>
       </c>
       <c r="F305" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
@@ -12088,19 +12088,19 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>Spanish III H</t>
+          <t>Spanish III</t>
         </is>
       </c>
       <c r="H306" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307">
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="F307" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         </is>
       </c>
       <c r="H307" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308">
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="H308" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="309">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="F309" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="H309" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="310">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="H310" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="311">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="F311" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="H311" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="312">
@@ -12306,12 +12306,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -12320,7 +12320,7 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="H312" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313">
@@ -12366,7 +12366,7 @@
         </is>
       </c>
       <c r="H313" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314">
@@ -12404,7 +12404,7 @@
         </is>
       </c>
       <c r="H314" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="315">
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="H315" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="316">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="F317" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="H318" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="319">
@@ -12572,29 +12572,29 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F319" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>World History</t>
+          <t>Introduction to Political Science</t>
         </is>
       </c>
       <c r="H319" s="4" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="H320" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="321">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F321" s="4" t="n">
@@ -12666,11 +12666,11 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Political Science</t>
+          <t>World History</t>
         </is>
       </c>
       <c r="H321" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="322">
@@ -12700,7 +12700,7 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="F323" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="H327" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="328">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
@@ -12932,11 +12932,11 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>Theology 10</t>
+          <t>Theology 9</t>
         </is>
       </c>
       <c r="H328" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -12962,15 +12962,15 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F329" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G329" s="5" t="inlineStr">
         <is>
-          <t>Theology 9</t>
+          <t>Theology 10</t>
         </is>
       </c>
       <c r="H329" s="4" t="n">
@@ -13000,19 +13000,19 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>Theology 9</t>
+          <t>Theology 10</t>
         </is>
       </c>
       <c r="H330" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="331">
@@ -13038,19 +13038,19 @@
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F331" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G331" s="5" t="inlineStr">
         <is>
-          <t>Theology 10</t>
+          <t>Theology 9</t>
         </is>
       </c>
       <c r="H331" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="332">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="H333" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="334">
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="H334" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="335">
@@ -13202,7 +13202,7 @@
         </is>
       </c>
       <c r="H335" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="H336" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="H337" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="338">
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="H338" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="339">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="F339" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H339" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="340">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="F340" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         </is>
       </c>
       <c r="H340" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="341">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="F341" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="F342" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         </is>
       </c>
       <c r="H342" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="343">
@@ -13506,7 +13506,7 @@
         </is>
       </c>
       <c r="H343" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="344">
@@ -13527,24 +13527,24 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>Journalism</t>
+          <t>British Literature</t>
         </is>
       </c>
       <c r="H344" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="345">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F345" s="4" t="n">
@@ -13578,11 +13578,11 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>Creative Writing</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="H345" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="346">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F346" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>British Literature</t>
+          <t>Creative Writing</t>
         </is>
       </c>
       <c r="H346" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -13646,11 +13646,11 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F347" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G347" s="5" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="H347" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="348">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -13684,11 +13684,11 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F348" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="H348" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="349">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -13734,7 +13734,7 @@
         </is>
       </c>
       <c r="H349" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="350">
@@ -13760,15 +13760,15 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F350" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>Algebra I</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="H350" s="2" t="n">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F351" s="4" t="n">
@@ -13806,11 +13806,11 @@
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Algebra I</t>
         </is>
       </c>
       <c r="H351" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="352">
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="H352" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="353">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="H354" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="355">
@@ -13962,7 +13962,7 @@
         </is>
       </c>
       <c r="H355" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="356">
@@ -14000,7 +14000,7 @@
         </is>
       </c>
       <c r="H356" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="357">
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="H357" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358">
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="H358" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="H360" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="361">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="H361" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="362">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="H362" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="363">
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="H363" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="364">
@@ -14304,7 +14304,7 @@
         </is>
       </c>
       <c r="H364" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365">
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="H366" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="367">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="H367" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="368">
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="H368" s="2" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="369">
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="H369" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="370">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="F370" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="H370" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="371">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>315</t>
         </is>
       </c>
       <c r="F371" s="4" t="n">
@@ -14566,11 +14566,11 @@
       </c>
       <c r="G371" s="5" t="inlineStr">
         <is>
-          <t>Italian I</t>
+          <t>Latin I H</t>
         </is>
       </c>
       <c r="H371" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -14596,19 +14596,19 @@
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>Latin I H</t>
+          <t>Italian I</t>
         </is>
       </c>
       <c r="H372" s="2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
